--- a/feature/modification-du-paragraphe-nomenclature/ig/CodeSystem-categorie-orientation-sas-codesystem.xlsx
+++ b/feature/modification-du-paragraphe-nomenclature/ig/CodeSystem-categorie-orientation-sas-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T15:48:30+00:00</t>
+    <t>2026-08-18T16:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/modification-du-paragraphe-nomenclature/ig/CodeSystem-categorie-orientation-sas-codesystem.xlsx
+++ b/feature/modification-du-paragraphe-nomenclature/ig/CodeSystem-categorie-orientation-sas-codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T16:06:46+00:00</t>
+    <t>2026-08-19T07:15:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
